--- a/Figure 6/Figure 6-D.xlsx
+++ b/Figure 6/Figure 6-D.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\图6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5CD5C9-65F3-466D-ABA1-C71554AAD937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E058505F-5FF6-476D-8A0E-047D2F0592F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31850" yWindow="6500" windowWidth="19500" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -126,7 +126,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +140,12 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -162,12 +168,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -458,231 +468,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="4">
         <v>1.7036740000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="4">
         <v>1.7186769999999996</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>1.5103020000000003</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5" s="4">
         <v>1.343602</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="4">
         <v>1.6786689999999993</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="4">
         <v>1.2202439999999997</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="4">
         <v>1.2735879999999993</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9" s="4">
         <v>2.1487630000000002</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="4">
         <v>1.278589</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="4">
         <v>1.9020469999999996</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="4">
         <v>1.5519769999999993</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="4">
         <v>1.4552909999999999</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="4">
         <v>1.18357</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="4">
         <v>1.6153229999999998</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="4">
         <v>1.4852970000000001</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="4">
         <v>1.3902779999999995</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="4">
         <v>1.9270520000000007</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="4">
         <v>1.2652530000000002</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="4">
         <v>1.7036739999999995</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="4">
         <v>1.091885</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="4">
         <v>1.5036339999999999</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="4">
         <v>1.6519970000000002</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="4">
         <v>1.5336399999999994</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="4">
         <v>1.6803360000000001</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="4">
         <v>1.9053809999999993</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="4">
         <v>2.0054009999999991</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="4">
         <v>1.940388</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="4">
         <v>1.3852769999999992</v>
       </c>
     </row>
